--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF7F636-C03E-4007-8F70-462FEFF6CB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27EAE8D-EC81-434F-8379-D928445A8BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="184">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -650,6 +650,116 @@
   </si>
   <si>
     <t>CheckDebuffTroop</t>
+  </si>
+  <si>
+    <t>落雷</t>
+  </si>
+  <si>
+    <t>妖术</t>
+  </si>
+  <si>
+    <t>ThunderboltCriticalMethod</t>
+  </si>
+  <si>
+    <t>SorcerySuccessMethod</t>
+  </si>
+  <si>
+    <t>SorceryCriticalMethod</t>
+  </si>
+  <si>
+    <t>技能视觉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ThunderboltSuccessMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visualType</t>
+  </si>
+  <si>
+    <t>Strategy</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Melee</t>
+  </si>
+  <si>
+    <t>CyclonSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ThunderboltSkill</t>
+  </si>
+  <si>
+    <t>[{
+          "class": "SetFire",
+          "probability": 10000,
+          "values": [
+            1,
+            2
+          ],
+          "weight": [
+            70,
+            30
+          ],
+          "condition": {
+            "class": "SkillIsCritical",
+            "result": 0
+          }
+        },
+        {
+          "class": "SetFire",
+          "probability": 10000,
+          "values": [
+            2,
+            3
+          ],
+          "weight": [
+            70,
+            30
+          ],
+          "condition": {
+            "class": "SkillIsCritical",
+            "result": 1
+          }
+        }]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[
+  {
+    "class": "TroopAddBuff",
+    "buffId": 1,
+    "probability": 5000,
+    "targetType": 1,
+    "values": [
+      2,
+      4
+    ],
+    "weight": [
+      70,
+      30
+    ]
+  },
+  {
+    "class": "TroopAddBuff",
+    "buffId": 2,
+    "probability": 5000,
+    "targetType": 1,
+    "values": [
+      2,
+      4
+    ],
+    "weight": [
+      70,
+      30
+    ]
+  }
+]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1133,7 +1243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
-  <dimension ref="A1:AK69"/>
+  <dimension ref="A1:AL69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.375" style="2" bestFit="1" customWidth="1"/>
@@ -1143,31 +1253,31 @@
     <col min="6" max="6" width="10.5" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.75" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.25" style="2" customWidth="1"/>
-    <col min="11" max="11" width="21.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="22.625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="255.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.25" style="2" customWidth="1"/>
-    <col min="22" max="22" width="19.75" style="2" customWidth="1"/>
-    <col min="23" max="23" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="25.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.25" style="2" customWidth="1"/>
-    <col min="31" max="31" width="70.5" style="2" customWidth="1"/>
-    <col min="32" max="16384" width="9" style="2"/>
+    <col min="9" max="10" width="16.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="25.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="21.875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="22.625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="255.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.25" style="2" customWidth="1"/>
+    <col min="23" max="23" width="19.75" style="2" customWidth="1"/>
+    <col min="24" max="24" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="25.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.25" style="2" customWidth="1"/>
+    <col min="32" max="32" width="70.5" style="2" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:38" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="12" t="s">
         <v>9</v>
@@ -1192,75 +1302,78 @@
         <v>80</v>
       </c>
       <c r="J1" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="L1" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="N1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="O1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="P1" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="Q1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="S1" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="T1" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="U1" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="U1" s="16"/>
-      <c r="V1" s="12" t="s">
+      <c r="V1" s="16"/>
+      <c r="W1" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="X1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="Y1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="Z1" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="Z1" s="12" t="s">
-        <v>41</v>
       </c>
       <c r="AA1" s="12" t="s">
         <v>41</v>
       </c>
       <c r="AB1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC1" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="AC1" s="12" t="s">
+      <c r="AD1" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="AD1" s="16" t="s">
+      <c r="AE1" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="8"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="8"/>
-      <c r="AK1" s="6"/>
-    </row>
-    <row r="2" spans="1:37" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="6"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="6"/>
+      <c r="AK1" s="8"/>
+      <c r="AL1" s="6"/>
+    </row>
+    <row r="2" spans="1:38" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1283,8 +1396,8 @@
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="3"/>
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
@@ -1292,16 +1405,17 @@
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="2"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="3"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
-    </row>
-    <row r="3" spans="1:37" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AL2" s="2"/>
+    </row>
+    <row r="3" spans="1:38" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1328,77 +1442,80 @@
         <v>81</v>
       </c>
       <c r="J3" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AC3" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AD3" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="AD3" s="7" t="s">
+      <c r="AE3" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
       <c r="AG3" s="7"/>
       <c r="AH3" s="7"/>
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
       <c r="AK3" s="7"/>
-    </row>
-    <row r="4" spans="1:37" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AL3" s="7"/>
+    </row>
+    <row r="4" spans="1:38" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1436,34 +1553,34 @@
         <v>87</v>
       </c>
       <c r="M4" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="N4" s="13" t="s">
         <v>4</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="O4" s="13" t="s">
         <v>65</v>
       </c>
       <c r="P4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="R4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="S4" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="T4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="U4" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="U4" s="14" t="s">
+      <c r="V4" s="14" t="s">
         <v>65</v>
-      </c>
-      <c r="V4" s="13" t="s">
-        <v>8</v>
       </c>
       <c r="W4" s="13" t="s">
         <v>8</v>
@@ -1484,13 +1601,16 @@
         <v>8</v>
       </c>
       <c r="AC4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD4" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="AD4" s="14" t="s">
+      <c r="AE4" s="14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1514,27 +1634,27 @@
         <v>100</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M5" s="4">
+      <c r="L5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N5" s="4">
         <v>1</v>
       </c>
-      <c r="N5" s="4">
+      <c r="O5" s="4">
         <v>0</v>
       </c>
-      <c r="O5" s="4"/>
-      <c r="P5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="U5" s="2" t="s">
+      <c r="P5" s="4"/>
+      <c r="Q5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="V5" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1545,7 +1665,7 @@
         <v>6</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="2" t="s">
         <v>7</v>
@@ -1553,15 +1673,18 @@
       <c r="AB5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD5" s="2" t="s">
+      <c r="AC5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE5" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="AF5" s="4"/>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
-      <c r="AJ5" s="4"/>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="AI5" s="4"/>
+      <c r="AK5" s="4"/>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1586,22 +1709,22 @@
         <v>100</v>
       </c>
       <c r="J6" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6" s="4">
         <v>2</v>
       </c>
-      <c r="N6" s="4">
+      <c r="O6" s="4">
         <v>0</v>
       </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="V6" s="2" t="s">
+      <c r="P6" s="4"/>
+      <c r="Q6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W6" s="2" t="s">
@@ -1614,7 +1737,7 @@
         <v>6</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA6" s="2" t="s">
         <v>7</v>
@@ -1622,15 +1745,18 @@
       <c r="AB6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD6" s="2" t="s">
+      <c r="AC6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE6" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="AF6" s="4"/>
       <c r="AG6" s="4"/>
       <c r="AH6" s="4"/>
-      <c r="AJ6" s="4"/>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="AI6" s="4"/>
+      <c r="AK6" s="4"/>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1656,38 +1782,38 @@
         <v>70</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M7" s="4">
-        <v>1</v>
+      <c r="L7" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="N7" s="4">
         <v>1</v>
       </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S7" s="2" t="s">
+      <c r="O7" s="4">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>7</v>
@@ -1701,15 +1827,18 @@
       <c r="AB7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE7" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AF7" s="4"/>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>
-      <c r="AJ7" s="4"/>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="AI7" s="4"/>
+      <c r="AK7" s="4"/>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1735,35 +1864,35 @@
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M8" s="4">
+      <c r="L8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N8" s="4">
         <v>1</v>
       </c>
-      <c r="N8" s="4">
+      <c r="O8" s="4">
         <v>2</v>
       </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="R8" s="2" t="s">
+      <c r="P8" s="4"/>
+      <c r="Q8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="V8" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8" s="2" t="s">
         <v>7</v>
@@ -1777,15 +1906,18 @@
       <c r="AB8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD8" s="2">
+      <c r="AC8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE8" s="2">
         <v>2838</v>
       </c>
-      <c r="AF8" s="4"/>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
-      <c r="AJ8" s="4"/>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="AI8" s="4"/>
+      <c r="AK8" s="4"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -1811,38 +1943,38 @@
         <v>60</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M9" s="4">
+      <c r="L9" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N9" s="4">
         <v>1</v>
       </c>
-      <c r="N9" s="4">
+      <c r="O9" s="4">
         <v>3</v>
       </c>
-      <c r="O9" s="4"/>
-      <c r="P9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S9" s="2" t="s">
+      <c r="P9" s="4"/>
+      <c r="Q9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="U9" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="U9" s="2" t="s">
+      <c r="V9" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="V9" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9" s="2" t="s">
         <v>7</v>
@@ -1856,15 +1988,18 @@
       <c r="AB9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD9" s="2" t="s">
+      <c r="AC9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE9" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AF9" s="4"/>
       <c r="AG9" s="4"/>
       <c r="AH9" s="4"/>
-      <c r="AJ9" s="4"/>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="AI9" s="4"/>
+      <c r="AK9" s="4"/>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -1890,35 +2025,35 @@
         <v>70</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M10" s="4">
-        <v>1</v>
+      <c r="L10" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="N10" s="4">
         <v>1</v>
       </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S10" s="2" t="s">
+      <c r="O10" s="4">
+        <v>1</v>
+      </c>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="V10" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="V10" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10" s="2" t="s">
         <v>7</v>
@@ -1932,15 +2067,18 @@
       <c r="AB10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD10" s="2">
+      <c r="AC10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE10" s="2">
         <v>2866</v>
       </c>
-      <c r="AF10" s="4"/>
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
-      <c r="AJ10" s="4"/>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="AI10" s="4"/>
+      <c r="AK10" s="4"/>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -1966,35 +2104,35 @@
         <v>70</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M11" s="4">
+      <c r="L11" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N11" s="4">
         <v>1</v>
       </c>
-      <c r="N11" s="4">
+      <c r="O11" s="4">
         <v>2</v>
       </c>
-      <c r="O11" s="4"/>
-      <c r="P11" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="P11" s="4"/>
       <c r="Q11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="V11" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="V11" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11" s="2" t="s">
         <v>7</v>
@@ -2008,15 +2146,18 @@
       <c r="AB11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD11" s="2" t="s">
+      <c r="AC11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE11" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="AF11" s="4"/>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
-      <c r="AJ11" s="4"/>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="AI11" s="4"/>
+      <c r="AK11" s="4"/>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2042,35 +2183,35 @@
         <v>65</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M12" s="4">
+      <c r="L12" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N12" s="4">
         <v>1</v>
       </c>
-      <c r="N12" s="4">
+      <c r="O12" s="4">
         <v>3</v>
       </c>
-      <c r="O12" s="4"/>
-      <c r="P12" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="P12" s="4"/>
       <c r="Q12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="V12" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>7</v>
@@ -2084,15 +2225,18 @@
       <c r="AB12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD12" s="2" t="s">
+      <c r="AC12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE12" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="AF12" s="4"/>
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
-      <c r="AJ12" s="4"/>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="AI12" s="4"/>
+      <c r="AK12" s="4"/>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2118,27 +2262,27 @@
         <v>75</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M13" s="4">
+      <c r="L13" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N13" s="4">
         <v>2</v>
       </c>
-      <c r="N13" s="4">
+      <c r="O13" s="4">
         <v>1</v>
       </c>
-      <c r="O13" s="4"/>
-      <c r="P13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R13" s="2" t="s">
+      <c r="P13" s="4"/>
+      <c r="Q13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S13" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="V13" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W13" s="2" t="s">
         <v>6</v>
       </c>
@@ -2149,7 +2293,7 @@
         <v>6</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA13" s="2" t="s">
         <v>7</v>
@@ -2157,15 +2301,18 @@
       <c r="AB13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD13" s="2" t="s">
+      <c r="AC13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE13" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AF13" s="4"/>
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
-      <c r="AJ13" s="4"/>
-    </row>
-    <row r="14" spans="1:37" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AI13" s="4"/>
+      <c r="AK13" s="4"/>
+    </row>
+    <row r="14" spans="1:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2191,30 +2338,30 @@
         <v>70</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="L14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M14" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="M14" s="4">
-        <v>2</v>
       </c>
       <c r="N14" s="4">
         <v>2</v>
       </c>
-      <c r="O14" s="4"/>
-      <c r="P14" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="O14" s="4">
+        <v>2</v>
+      </c>
+      <c r="P14" s="4"/>
       <c r="Q14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="V14" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W14" s="2" t="s">
         <v>6</v>
       </c>
@@ -2225,7 +2372,7 @@
         <v>6</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA14" s="2" t="s">
         <v>7</v>
@@ -2233,15 +2380,18 @@
       <c r="AB14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD14" s="2" t="s">
+      <c r="AC14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE14" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AF14" s="4"/>
       <c r="AG14" s="4"/>
       <c r="AH14" s="4"/>
-      <c r="AJ14" s="4"/>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="AI14" s="4"/>
+      <c r="AK14" s="4"/>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2267,27 +2417,27 @@
         <v>65</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M15" s="4">
+      <c r="L15" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N15" s="4">
         <v>2</v>
       </c>
-      <c r="N15" s="4">
+      <c r="O15" s="4">
         <v>3</v>
       </c>
-      <c r="O15" s="4"/>
-      <c r="P15" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="P15" s="4"/>
       <c r="Q15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="V15" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W15" s="2" t="s">
         <v>6</v>
       </c>
@@ -2298,7 +2448,7 @@
         <v>6</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA15" s="2" t="s">
         <v>7</v>
@@ -2306,15 +2456,18 @@
       <c r="AB15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD15" s="2" t="s">
+      <c r="AC15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE15" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AF15" s="4"/>
       <c r="AG15" s="4"/>
       <c r="AH15" s="4"/>
-      <c r="AJ15" s="4"/>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="AI15" s="4"/>
+      <c r="AK15" s="4"/>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2340,35 +2493,35 @@
         <v>70</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M16" s="4">
-        <v>1</v>
+      <c r="L16" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="N16" s="4">
         <v>1</v>
       </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S16" s="2" t="s">
+      <c r="O16" s="4">
+        <v>1</v>
+      </c>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="U16" s="2" t="s">
+      <c r="V16" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="V16" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16" s="2" t="s">
         <v>7</v>
@@ -2382,15 +2535,18 @@
       <c r="AB16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD16" s="2" t="s">
+      <c r="AC16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE16" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="AF16" s="4"/>
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
-      <c r="AJ16" s="4"/>
-    </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI16" s="4"/>
+      <c r="AK16" s="4"/>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2416,35 +2572,35 @@
         <v>65</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M17" s="4">
+      <c r="L17" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="4">
         <v>1</v>
       </c>
-      <c r="N17" s="4">
+      <c r="O17" s="4">
         <v>2</v>
       </c>
-      <c r="O17" s="4"/>
-      <c r="P17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S17" s="2" t="s">
+      <c r="P17" s="4"/>
+      <c r="Q17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="U17" s="2" t="s">
+      <c r="V17" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="V17" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17" s="2" t="s">
         <v>7</v>
@@ -2458,15 +2614,18 @@
       <c r="AB17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD17" s="2" t="s">
+      <c r="AC17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE17" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="AF17" s="4"/>
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
-      <c r="AJ17" s="4"/>
-    </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI17" s="4"/>
+      <c r="AK17" s="4"/>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2492,35 +2651,35 @@
         <v>60</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M18" s="4">
+      <c r="L18" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N18" s="4">
         <v>1</v>
       </c>
-      <c r="N18" s="4">
+      <c r="O18" s="4">
         <v>3</v>
       </c>
-      <c r="O18" s="4"/>
-      <c r="P18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S18" s="2" t="s">
+      <c r="P18" s="4"/>
+      <c r="Q18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T18" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="U18" s="2" t="s">
+      <c r="V18" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="V18" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y18" s="2" t="s">
         <v>7</v>
@@ -2534,15 +2693,18 @@
       <c r="AB18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD18" s="2" t="s">
+      <c r="AC18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE18" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="AF18" s="4"/>
       <c r="AG18" s="4"/>
       <c r="AH18" s="4"/>
-      <c r="AJ18" s="4"/>
-    </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI18" s="4"/>
+      <c r="AK18" s="4"/>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2568,40 +2730,40 @@
         <v>100</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M19" s="4">
+      <c r="L19" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N19" s="4">
         <v>2</v>
       </c>
-      <c r="N19" s="4">
+      <c r="O19" s="4">
         <v>0</v>
       </c>
-      <c r="O19" s="4">
-        <v>7</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R19" s="2" t="s">
+      <c r="P19" s="4">
+        <v>7</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S19" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="V19" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA19" s="2" t="s">
         <v>7</v>
@@ -2609,15 +2771,18 @@
       <c r="AB19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD19" s="2" t="s">
+      <c r="AC19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AF19" s="4"/>
       <c r="AG19" s="4"/>
       <c r="AH19" s="4"/>
-      <c r="AJ19" s="4"/>
-    </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI19" s="4"/>
+      <c r="AK19" s="4"/>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -2643,24 +2808,24 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M20" s="4">
+      <c r="L20" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N20" s="4">
         <v>1</v>
       </c>
-      <c r="N20" s="4">
+      <c r="O20" s="4">
         <v>0</v>
       </c>
-      <c r="O20" s="4">
-        <v>6</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="V20" s="2" t="s">
+      <c r="P20" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="W20" s="2" t="s">
@@ -2670,10 +2835,10 @@
         <v>7</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA20" s="2" t="s">
         <v>7</v>
@@ -2681,15 +2846,18 @@
       <c r="AB20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD20" s="2" t="s">
+      <c r="AC20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="AF20" s="4"/>
       <c r="AG20" s="4"/>
       <c r="AH20" s="4"/>
-      <c r="AJ20" s="4"/>
-    </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI20" s="4"/>
+      <c r="AK20" s="4"/>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -2715,40 +2883,40 @@
         <v>100</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M21" s="4">
+      <c r="L21" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N21" s="4">
         <v>1</v>
       </c>
-      <c r="N21" s="4">
+      <c r="O21" s="4">
         <v>0</v>
       </c>
-      <c r="O21" s="4">
+      <c r="P21" s="4">
         <v>9</v>
       </c>
-      <c r="P21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R21" s="2" t="s">
+      <c r="Q21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S21" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="V21" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA21" s="2" t="s">
         <v>7</v>
@@ -2756,15 +2924,18 @@
       <c r="AB21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD21" s="2" t="s">
+      <c r="AC21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE21" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="AF21" s="4"/>
       <c r="AG21" s="4"/>
       <c r="AH21" s="4"/>
-      <c r="AJ21" s="4"/>
-    </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI21" s="4"/>
+      <c r="AK21" s="4"/>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -2790,29 +2961,29 @@
         <v>100</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="L22" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N22" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="N22" s="4">
+      <c r="O22" s="4">
         <v>0</v>
       </c>
-      <c r="O22" s="4">
+      <c r="P22" s="4">
         <v>8</v>
       </c>
-      <c r="P22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="Q22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="V22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W22" s="2" t="s">
         <v>6</v>
       </c>
@@ -2823,7 +2994,7 @@
         <v>6</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA22" s="2" t="s">
         <v>7</v>
@@ -2831,15 +3002,18 @@
       <c r="AB22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD22" s="2" t="s">
+      <c r="AC22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE22" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="AF22" s="4"/>
       <c r="AG22" s="4"/>
       <c r="AH22" s="4"/>
-      <c r="AJ22" s="4"/>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI22" s="4"/>
+      <c r="AK22" s="4"/>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -2865,29 +3039,29 @@
         <v>100</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M23" s="4">
+      <c r="L23" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N23" s="4">
         <v>2</v>
       </c>
-      <c r="N23" s="4">
+      <c r="O23" s="4">
         <v>1</v>
       </c>
-      <c r="O23" s="4">
+      <c r="P23" s="4">
         <v>10</v>
       </c>
-      <c r="P23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S23" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="V23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W23" s="2" t="s">
         <v>6</v>
       </c>
@@ -2898,7 +3072,7 @@
         <v>6</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA23" s="2" t="s">
         <v>7</v>
@@ -2906,15 +3080,18 @@
       <c r="AB23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD23" s="2" t="s">
+      <c r="AC23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE23" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="AF23" s="4"/>
       <c r="AG23" s="4"/>
       <c r="AH23" s="4"/>
-      <c r="AJ23" s="4"/>
-    </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI23" s="4"/>
+      <c r="AK23" s="4"/>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -2940,29 +3117,29 @@
         <v>70</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M24" s="4">
+      <c r="L24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N24" s="4">
         <v>1</v>
       </c>
-      <c r="N24" s="4">
+      <c r="O24" s="4">
         <v>2</v>
       </c>
-      <c r="O24" s="4">
+      <c r="P24" s="4">
         <v>11</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T24" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="V24" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W24" s="2" t="s">
         <v>6</v>
       </c>
@@ -2973,7 +3150,7 @@
         <v>6</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA24" s="2" t="s">
         <v>7</v>
@@ -2981,15 +3158,18 @@
       <c r="AB24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD24" s="2" t="s">
+      <c r="AC24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE24" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="AF24" s="4"/>
       <c r="AG24" s="4"/>
       <c r="AH24" s="4"/>
-      <c r="AJ24" s="4"/>
-    </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI24" s="4"/>
+      <c r="AK24" s="4"/>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -3015,29 +3195,29 @@
         <v>100</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M25" s="4" t="s">
+      <c r="L25" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N25" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="N25" s="4">
+      <c r="O25" s="4">
         <v>3</v>
       </c>
-      <c r="O25" s="4">
+      <c r="P25" s="4">
         <v>12</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="Q25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="V25" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W25" s="2" t="s">
         <v>6</v>
       </c>
@@ -3048,7 +3228,7 @@
         <v>6</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA25" s="2" t="s">
         <v>7</v>
@@ -3056,15 +3236,18 @@
       <c r="AB25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD25" s="2" t="s">
+      <c r="AC25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE25" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AF25" s="4"/>
       <c r="AG25" s="4"/>
       <c r="AH25" s="4"/>
-      <c r="AJ25" s="4"/>
-    </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI25" s="4"/>
+      <c r="AK25" s="4"/>
+    </row>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -3090,27 +3273,27 @@
         <v>0</v>
       </c>
       <c r="J26" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K26" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K26" s="4" t="s">
+      <c r="L26" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="M26" s="4">
+      <c r="N26" s="4">
         <v>1</v>
       </c>
-      <c r="N26" s="4">
+      <c r="O26" s="4">
         <v>0</v>
       </c>
-      <c r="O26" s="4"/>
-      <c r="P26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R26" s="2" t="s">
+      <c r="P26" s="4"/>
+      <c r="Q26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S26" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="V26" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W26" s="2" t="s">
         <v>6</v>
       </c>
@@ -3121,23 +3304,26 @@
         <v>6</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA26" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE26" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="AF26" s="4"/>
       <c r="AG26" s="4"/>
       <c r="AH26" s="4"/>
-      <c r="AJ26" s="4"/>
-    </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI26" s="4"/>
+      <c r="AK26" s="4"/>
+    </row>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -3159,30 +3345,30 @@
         <v>0</v>
       </c>
       <c r="J27" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K27" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="K27" s="4" t="s">
+      <c r="L27" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="M27" s="4">
+      <c r="N27" s="4">
         <v>1</v>
       </c>
-      <c r="N27" s="4">
+      <c r="O27" s="4">
         <v>0</v>
       </c>
-      <c r="O27" s="4"/>
-      <c r="P27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R27" s="2" t="s">
+      <c r="P27" s="4"/>
+      <c r="Q27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S27" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="U27" s="2" t="s">
+      <c r="V27" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="V27" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W27" s="2" t="s">
         <v>6</v>
       </c>
@@ -3193,26 +3379,29 @@
         <v>6</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA27" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AC27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD27" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AD27" s="2" t="s">
+      <c r="AE27" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AF27" s="4"/>
       <c r="AG27" s="4"/>
       <c r="AH27" s="4"/>
-      <c r="AJ27" s="4"/>
-    </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI27" s="4"/>
+      <c r="AK27" s="4"/>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>129</v>
       </c>
@@ -3239,30 +3428,30 @@
         <v>0</v>
       </c>
       <c r="J28" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="L28" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="M28" s="4" t="s">
+      <c r="N28" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="N28" s="4">
+      <c r="O28" s="4">
         <v>0</v>
       </c>
-      <c r="O28" s="4"/>
-      <c r="P28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R28" s="2" t="s">
+      <c r="P28" s="4"/>
+      <c r="Q28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S28" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="U28" s="2" t="s">
+      <c r="V28" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="V28" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W28" s="2" t="s">
         <v>6</v>
       </c>
@@ -3270,7 +3459,7 @@
         <v>6</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>7</v>
@@ -3281,15 +3470,18 @@
       <c r="AB28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD28" s="2" t="s">
+      <c r="AC28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE28" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AF28" s="4"/>
       <c r="AG28" s="4"/>
       <c r="AH28" s="4"/>
-      <c r="AJ28" s="4"/>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI28" s="4"/>
+      <c r="AK28" s="4"/>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3313,30 +3505,30 @@
         <v>0</v>
       </c>
       <c r="J29" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="L29" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="M29" s="4" t="s">
+      <c r="N29" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="N29" s="4">
+      <c r="O29" s="4">
         <v>0</v>
       </c>
-      <c r="O29" s="4"/>
-      <c r="P29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R29" s="2" t="s">
+      <c r="P29" s="4"/>
+      <c r="Q29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S29" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U29" s="2" t="s">
+      <c r="V29" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="V29" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W29" s="2" t="s">
         <v>6</v>
       </c>
@@ -3344,7 +3536,7 @@
         <v>6</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>7</v>
@@ -3355,15 +3547,18 @@
       <c r="AB29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD29" s="2" t="s">
+      <c r="AC29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE29" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AF29" s="4"/>
       <c r="AG29" s="4"/>
       <c r="AH29" s="4"/>
-      <c r="AJ29" s="4"/>
-    </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI29" s="4"/>
+      <c r="AK29" s="4"/>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3385,30 +3580,30 @@
         <v>0</v>
       </c>
       <c r="J30" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K30" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="K30" s="4" t="s">
+      <c r="L30" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="M30" s="4" t="s">
+      <c r="N30" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="N30" s="4">
+      <c r="O30" s="4">
         <v>0</v>
       </c>
-      <c r="O30" s="4"/>
-      <c r="P30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R30" s="2" t="s">
+      <c r="P30" s="4"/>
+      <c r="Q30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S30" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="U30" s="2" t="s">
+      <c r="V30" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="V30" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W30" s="2" t="s">
         <v>6</v>
       </c>
@@ -3416,29 +3611,32 @@
         <v>6</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA30" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB30" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD30" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="AD30" s="2" t="s">
+      <c r="AE30" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="AF30" s="4"/>
       <c r="AG30" s="4"/>
       <c r="AH30" s="4"/>
-      <c r="AJ30" s="4"/>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI30" s="4"/>
+      <c r="AK30" s="4"/>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -3462,27 +3660,27 @@
         <v>0</v>
       </c>
       <c r="J31" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K31" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="L31" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="M31" s="4">
+      <c r="N31" s="4">
         <v>1</v>
       </c>
-      <c r="N31" s="4">
+      <c r="O31" s="4">
         <v>0</v>
       </c>
-      <c r="O31" s="4"/>
-      <c r="P31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="U31" s="2" t="s">
+      <c r="P31" s="4"/>
+      <c r="Q31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V31" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="V31" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W31" s="2" t="s">
         <v>6</v>
       </c>
@@ -3490,7 +3688,7 @@
         <v>6</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z31" s="2" t="s">
         <v>7</v>
@@ -3501,15 +3699,18 @@
       <c r="AB31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD31" s="2" t="s">
+      <c r="AC31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE31" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AF31" s="4"/>
       <c r="AG31" s="4"/>
       <c r="AH31" s="4"/>
-      <c r="AJ31" s="4"/>
-    </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI31" s="4"/>
+      <c r="AK31" s="4"/>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -3533,27 +3734,27 @@
         <v>0</v>
       </c>
       <c r="J32" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K32" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="K32" s="4" t="s">
+      <c r="L32" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="M32" s="4">
+      <c r="N32" s="4">
         <v>1</v>
       </c>
-      <c r="N32" s="4">
+      <c r="O32" s="4">
         <v>0</v>
       </c>
-      <c r="O32" s="4"/>
-      <c r="P32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="U32" s="2" t="s">
+      <c r="P32" s="4"/>
+      <c r="Q32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V32" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="V32" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W32" s="2" t="s">
         <v>6</v>
       </c>
@@ -3561,7 +3762,7 @@
         <v>6</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>7</v>
@@ -3572,53 +3773,182 @@
       <c r="AB32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD32" s="2" t="s">
+      <c r="AC32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE32" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AF32" s="4"/>
       <c r="AG32" s="4"/>
       <c r="AH32" s="4"/>
-      <c r="AJ32" s="4"/>
-    </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="AF33" s="4"/>
+      <c r="AI32" s="4"/>
+      <c r="AK32" s="4"/>
+    </row>
+    <row r="33" spans="2:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="4">
+        <v>29</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="4">
+        <v>3</v>
+      </c>
+      <c r="F33" s="4">
+        <v>40</v>
+      </c>
+      <c r="G33" s="4">
+        <v>5</v>
+      </c>
+      <c r="H33" s="4">
+        <v>50</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="O33" s="4">
+        <v>0</v>
+      </c>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE33" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="AG33" s="4"/>
       <c r="AH33" s="4"/>
-      <c r="AJ33" s="4"/>
-    </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="AF34" s="4"/>
+      <c r="AI33" s="4"/>
+      <c r="AK33" s="4"/>
+    </row>
+    <row r="34" spans="2:37" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="4">
+        <v>30</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" s="4">
+        <v>3</v>
+      </c>
+      <c r="F34" s="4">
+        <v>25</v>
+      </c>
+      <c r="G34" s="4">
+        <v>5</v>
+      </c>
+      <c r="H34" s="4">
+        <v>30</v>
+      </c>
+      <c r="I34" s="4">
+        <v>0</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="O34" s="4">
+        <v>0</v>
+      </c>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE34" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="AG34" s="4"/>
       <c r="AH34" s="4"/>
-      <c r="AJ34" s="4"/>
-    </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI34" s="4"/>
+      <c r="AK34" s="4"/>
+    </row>
+    <row r="35" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -3629,15 +3959,16 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
-      <c r="M35" s="4"/>
+      <c r="L35" s="4"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
-      <c r="AF35" s="4"/>
+      <c r="P35" s="4"/>
       <c r="AG35" s="4"/>
       <c r="AH35" s="4"/>
-      <c r="AJ35" s="4"/>
-    </row>
-    <row r="36" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI35" s="4"/>
+      <c r="AK35" s="4"/>
+    </row>
+    <row r="36" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -3648,15 +3979,16 @@
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="M36" s="4"/>
+      <c r="L36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
-      <c r="AF36" s="4"/>
+      <c r="P36" s="4"/>
       <c r="AG36" s="4"/>
       <c r="AH36" s="4"/>
-      <c r="AJ36" s="4"/>
-    </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI36" s="4"/>
+      <c r="AK36" s="4"/>
+    </row>
+    <row r="37" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -3667,15 +3999,16 @@
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
-      <c r="M37" s="4"/>
+      <c r="L37" s="4"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
-      <c r="AF37" s="4"/>
+      <c r="P37" s="4"/>
       <c r="AG37" s="4"/>
       <c r="AH37" s="4"/>
-      <c r="AJ37" s="4"/>
-    </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI37" s="4"/>
+      <c r="AK37" s="4"/>
+    </row>
+    <row r="38" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -3686,15 +4019,16 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
-      <c r="M38" s="4"/>
+      <c r="L38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-      <c r="AF38" s="4"/>
+      <c r="P38" s="4"/>
       <c r="AG38" s="4"/>
       <c r="AH38" s="4"/>
-      <c r="AJ38" s="4"/>
-    </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI38" s="4"/>
+      <c r="AK38" s="4"/>
+    </row>
+    <row r="39" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3705,15 +4039,16 @@
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
-      <c r="M39" s="4"/>
+      <c r="L39" s="4"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
-      <c r="AF39" s="4"/>
+      <c r="P39" s="4"/>
       <c r="AG39" s="4"/>
       <c r="AH39" s="4"/>
-      <c r="AJ39" s="4"/>
-    </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI39" s="4"/>
+      <c r="AK39" s="4"/>
+    </row>
+    <row r="40" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3724,15 +4059,16 @@
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
-      <c r="M40" s="4"/>
+      <c r="L40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="AF40" s="4"/>
+      <c r="P40" s="4"/>
       <c r="AG40" s="4"/>
       <c r="AH40" s="4"/>
-      <c r="AJ40" s="4"/>
-    </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI40" s="4"/>
+      <c r="AK40" s="4"/>
+    </row>
+    <row r="41" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3743,15 +4079,16 @@
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
-      <c r="M41" s="4"/>
+      <c r="L41" s="4"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
-      <c r="AF41" s="4"/>
+      <c r="P41" s="4"/>
       <c r="AG41" s="4"/>
       <c r="AH41" s="4"/>
-      <c r="AJ41" s="4"/>
-    </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI41" s="4"/>
+      <c r="AK41" s="4"/>
+    </row>
+    <row r="42" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -3762,15 +4099,16 @@
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
-      <c r="M42" s="4"/>
+      <c r="L42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="AF42" s="4"/>
+      <c r="P42" s="4"/>
       <c r="AG42" s="4"/>
       <c r="AH42" s="4"/>
-      <c r="AJ42" s="4"/>
-    </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI42" s="4"/>
+      <c r="AK42" s="4"/>
+    </row>
+    <row r="43" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -3781,15 +4119,16 @@
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
-      <c r="M43" s="4"/>
+      <c r="L43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
-      <c r="AF43" s="4"/>
+      <c r="P43" s="4"/>
       <c r="AG43" s="4"/>
       <c r="AH43" s="4"/>
-      <c r="AJ43" s="4"/>
-    </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI43" s="4"/>
+      <c r="AK43" s="4"/>
+    </row>
+    <row r="44" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -3800,40 +4139,41 @@
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
-      <c r="M44" s="4"/>
+      <c r="L44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="AF44" s="4"/>
+      <c r="P44" s="4"/>
       <c r="AG44" s="4"/>
       <c r="AH44" s="4"/>
-      <c r="AJ44" s="4"/>
-    </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI44" s="4"/>
+      <c r="AK44" s="4"/>
+    </row>
+    <row r="45" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="AF45" s="4"/>
       <c r="AG45" s="4"/>
       <c r="AH45" s="4"/>
-      <c r="AJ45" s="4"/>
-    </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AI45" s="4"/>
+      <c r="AK45" s="4"/>
+    </row>
+    <row r="46" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-      <c r="AF46" s="4"/>
-      <c r="AH46" s="4"/>
-      <c r="AJ46" s="4"/>
-    </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="AG46" s="4"/>
+      <c r="AI46" s="4"/>
+      <c r="AK46" s="4"/>
+    </row>
+    <row r="47" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27EAE8D-EC81-434F-8379-D928445A8BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7EDA7A-2915-455C-8D9A-C5E1D11F1CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="186">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -759,6 +759,14 @@
     ]
   }
 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canTriggerDuel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能否触发单挑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1365,7 +1373,9 @@
       <c r="AE1" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="AF1" s="6"/>
+      <c r="AF1" s="6" t="s">
+        <v>185</v>
+      </c>
       <c r="AG1" s="8"/>
       <c r="AH1" s="6"/>
       <c r="AI1" s="8"/>
@@ -1507,7 +1517,9 @@
       <c r="AE3" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="AF3" s="7"/>
+      <c r="AF3" s="7" t="s">
+        <v>184</v>
+      </c>
       <c r="AG3" s="7"/>
       <c r="AH3" s="7"/>
       <c r="AI3" s="7"/>
@@ -1609,6 +1621,9 @@
       <c r="AE4" s="14" t="s">
         <v>4</v>
       </c>
+      <c r="AF4" s="10" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
@@ -1678,6 +1693,9 @@
       </c>
       <c r="AE5" s="2" t="s">
         <v>144</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -1751,6 +1769,9 @@
       <c r="AE6" s="2" t="s">
         <v>143</v>
       </c>
+      <c r="AF6" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG6" s="4"/>
       <c r="AH6" s="4"/>
       <c r="AI6" s="4"/>
@@ -1833,6 +1854,9 @@
       <c r="AE7" s="2" t="s">
         <v>141</v>
       </c>
+      <c r="AF7" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>
       <c r="AI7" s="4"/>
@@ -1912,6 +1936,9 @@
       <c r="AE8" s="2">
         <v>2838</v>
       </c>
+      <c r="AF8" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
       <c r="AI8" s="4"/>
@@ -1994,6 +2021,9 @@
       <c r="AE9" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="AF9" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG9" s="4"/>
       <c r="AH9" s="4"/>
       <c r="AI9" s="4"/>
@@ -2073,6 +2103,9 @@
       <c r="AE10" s="2">
         <v>2866</v>
       </c>
+      <c r="AF10" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
       <c r="AI10" s="4"/>
@@ -2152,6 +2185,9 @@
       <c r="AE11" s="2" t="s">
         <v>142</v>
       </c>
+      <c r="AF11" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
       <c r="AI11" s="4"/>
@@ -2231,6 +2267,9 @@
       <c r="AE12" s="2" t="s">
         <v>142</v>
       </c>
+      <c r="AF12" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
       <c r="AI12" s="4"/>
@@ -2307,6 +2346,9 @@
       <c r="AE13" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="AF13" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
       <c r="AI13" s="4"/>
@@ -2386,6 +2428,9 @@
       <c r="AE14" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="AF14" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG14" s="4"/>
       <c r="AH14" s="4"/>
       <c r="AI14" s="4"/>
@@ -2462,6 +2507,9 @@
       <c r="AE15" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="AF15" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG15" s="4"/>
       <c r="AH15" s="4"/>
       <c r="AI15" s="4"/>
@@ -2541,6 +2589,9 @@
       <c r="AE16" s="2" t="s">
         <v>138</v>
       </c>
+      <c r="AF16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
       <c r="AI16" s="4"/>
@@ -2620,6 +2671,9 @@
       <c r="AE17" s="2" t="s">
         <v>137</v>
       </c>
+      <c r="AF17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
       <c r="AI17" s="4"/>
@@ -2699,6 +2753,9 @@
       <c r="AE18" s="2" t="s">
         <v>138</v>
       </c>
+      <c r="AF18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="AG18" s="4"/>
       <c r="AH18" s="4"/>
       <c r="AI18" s="4"/>
@@ -2777,6 +2834,9 @@
       <c r="AE19" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="AF19" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG19" s="4"/>
       <c r="AH19" s="4"/>
       <c r="AI19" s="4"/>
@@ -2852,6 +2912,9 @@
       <c r="AE20" s="2" t="s">
         <v>142</v>
       </c>
+      <c r="AF20" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG20" s="4"/>
       <c r="AH20" s="4"/>
       <c r="AI20" s="4"/>
@@ -2930,6 +2993,9 @@
       <c r="AE21" s="2" t="s">
         <v>146</v>
       </c>
+      <c r="AF21" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG21" s="4"/>
       <c r="AH21" s="4"/>
       <c r="AI21" s="4"/>
@@ -3008,6 +3074,9 @@
       <c r="AE22" s="2" t="s">
         <v>139</v>
       </c>
+      <c r="AF22" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG22" s="4"/>
       <c r="AH22" s="4"/>
       <c r="AI22" s="4"/>
@@ -3086,6 +3155,9 @@
       <c r="AE23" s="2" t="s">
         <v>145</v>
       </c>
+      <c r="AF23" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG23" s="4"/>
       <c r="AH23" s="4"/>
       <c r="AI23" s="4"/>
@@ -3164,6 +3236,9 @@
       <c r="AE24" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="AF24" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG24" s="4"/>
       <c r="AH24" s="4"/>
       <c r="AI24" s="4"/>
@@ -3242,6 +3317,9 @@
       <c r="AE25" s="2" t="s">
         <v>147</v>
       </c>
+      <c r="AF25" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG25" s="4"/>
       <c r="AH25" s="4"/>
       <c r="AI25" s="4"/>
@@ -3318,6 +3396,9 @@
       <c r="AE26" s="2" t="s">
         <v>149</v>
       </c>
+      <c r="AF26" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG26" s="4"/>
       <c r="AH26" s="4"/>
       <c r="AI26" s="4"/>
@@ -3396,6 +3477,9 @@
       <c r="AE27" s="2" t="s">
         <v>147</v>
       </c>
+      <c r="AF27" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG27" s="4"/>
       <c r="AH27" s="4"/>
       <c r="AI27" s="4"/>
@@ -3476,6 +3560,9 @@
       <c r="AE28" s="2" t="s">
         <v>141</v>
       </c>
+      <c r="AF28" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG28" s="4"/>
       <c r="AH28" s="4"/>
       <c r="AI28" s="4"/>
@@ -3553,6 +3640,9 @@
       <c r="AE29" s="2" t="s">
         <v>141</v>
       </c>
+      <c r="AF29" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG29" s="4"/>
       <c r="AH29" s="4"/>
       <c r="AI29" s="4"/>
@@ -3631,6 +3721,9 @@
       <c r="AE30" s="2" t="s">
         <v>140</v>
       </c>
+      <c r="AF30" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG30" s="4"/>
       <c r="AH30" s="4"/>
       <c r="AI30" s="4"/>
@@ -3705,6 +3798,9 @@
       <c r="AE31" s="2" t="s">
         <v>141</v>
       </c>
+      <c r="AF31" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG31" s="4"/>
       <c r="AH31" s="4"/>
       <c r="AI31" s="4"/>
@@ -3779,6 +3875,9 @@
       <c r="AE32" s="2" t="s">
         <v>141</v>
       </c>
+      <c r="AF32" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG32" s="4"/>
       <c r="AH32" s="4"/>
       <c r="AI32" s="4"/>
@@ -3861,6 +3960,9 @@
       <c r="AE33" s="2" t="s">
         <v>141</v>
       </c>
+      <c r="AF33" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="AG33" s="4"/>
       <c r="AH33" s="4"/>
       <c r="AI33" s="4"/>
@@ -3942,6 +4044,9 @@
       </c>
       <c r="AE34" s="2" t="s">
         <v>141</v>
+      </c>
+      <c r="AF34" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="AG34" s="4"/>
       <c r="AH34" s="4"/>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7EDA7A-2915-455C-8D9A-C5E1D11F1CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83901AE-5FDD-43AB-806F-37B504742896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="187">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -729,45 +729,36 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>canTriggerDuel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能否触发单挑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[
-  {
-    "class": "TroopAddBuff",
-    "buffId": 1,
-    "probability": 5000,
-    "targetType": 1,
-    "values": [
-      2,
-      4
-    ],
-    "weight": [
-      70,
-      30
-    ]
-  },
-  {
-    "class": "TroopAddBuff",
-    "buffId": 2,
-    "probability": 5000,
-    "targetType": 1,
-    "values": [
-      2,
-      4
-    ],
-    "weight": [
-      70,
-      30
-    ]
-  }
-]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>canTriggerDuel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>能否触发单挑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+        {
+          "class": "AddBuffRandom",
+          "buffIds": [
+            1,
+            2
+          ],
+          "probability": 10000,
+          "values": [
+            2,
+            4
+          ],
+          "weight": [
+            70,
+            30
+          ]
+        }
+      ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DemonSkill</t>
   </si>
 </sst>
 </file>
@@ -1374,7 +1365,7 @@
         <v>133</v>
       </c>
       <c r="AF1" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG1" s="8"/>
       <c r="AH1" s="6"/>
@@ -1518,7 +1509,7 @@
         <v>134</v>
       </c>
       <c r="AF3" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG3" s="7"/>
       <c r="AH3" s="7"/>
@@ -3897,7 +3888,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G33" s="4">
         <v>5</v>
@@ -3982,19 +3973,19 @@
         <v>3</v>
       </c>
       <c r="F34" s="4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G34" s="4">
         <v>5</v>
       </c>
       <c r="H34" s="4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I34" s="4">
         <v>0</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>172</v>
@@ -4016,7 +4007,7 @@
         <v>63</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="V34" s="2" t="s">
         <v>152</v>
@@ -4031,13 +4022,13 @@
         <v>6</v>
       </c>
       <c r="Z34" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB34" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC34" s="2" t="s">
         <v>7</v>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="188">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -759,6 +759,38 @@
   </si>
   <si>
     <t>DemonSkill</t>
+  </si>
+  <si>
+    <t>[
+  {
+    "class": "TroopAddBuff",
+    "buffId": 1,
+    "probability": 5000,
+    "targetType": 1,
+    "values": [
+      2,
+      4
+    ],
+    "weight": [
+      70,
+      30
+    ]
+  },
+  {
+    "class": "TroopAddBuff",
+    "buffId": 2,
+    "probability": 5000,
+    "targetType": 1,
+    "values": [
+      2,
+      4
+    ],
+    "weight": [
+      70,
+      30
+    ]
+  }
+]</t>
   </si>
 </sst>
 </file>
@@ -3888,7 +3920,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G33" s="4">
         <v>5</v>
@@ -3973,19 +4005,19 @@
         <v>3</v>
       </c>
       <c r="F34" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G34" s="4">
         <v>5</v>
       </c>
       <c r="H34" s="4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I34" s="4">
         <v>0</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>172</v>
@@ -4007,7 +4039,7 @@
         <v>63</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="V34" s="2" t="s">
         <v>152</v>
@@ -4022,13 +4054,13 @@
         <v>6</v>
       </c>
       <c r="Z34" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA34" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB34" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC34" s="2" t="s">
         <v>7</v>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83901AE-5FDD-43AB-806F-37B504742896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA16F20-66B6-47D9-9CAB-8F883A4348A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4620" yWindow="1635" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="186">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -735,30 +735,6 @@
   <si>
     <t>能否触发单挑</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[
-        {
-          "class": "AddBuffRandom",
-          "buffIds": [
-            1,
-            2
-          ],
-          "probability": 10000,
-          "values": [
-            2,
-            4
-          ],
-          "weight": [
-            70,
-            30
-          ]
-        }
-      ]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DemonSkill</t>
   </si>
   <si>
     <t>[
@@ -3365,7 +3341,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H26" s="4">
         <v>10</v>
@@ -4039,7 +4015,7 @@
         <v>63</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="V34" s="2" t="s">
         <v>152</v>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA16F20-66B6-47D9-9CAB-8F883A4348A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3143BD-35E7-41AB-ADE5-9870F467A936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="1635" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="36" r:id="rId1"/>
@@ -3338,10 +3338,10 @@
         <v>3</v>
       </c>
       <c r="F26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="4">
         <v>10</v>
